--- a/jd.xlsx
+++ b/jd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEI XIAO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE641A6F-3E01-4BAB-A4B1-7A7018D20543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D1CA76-CCBF-48E1-B7EB-62B7651C3C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15074,12 +15074,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>商品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>条码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>name</t>
+  </si>
+  <si>
+    <t>barcode</t>
   </si>
 </sst>
 </file>
